--- a/2026夏制作資料/夏制作コスト表.xlsx
+++ b/2026夏制作資料/夏制作コスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hirot\Desktop\iroiro\unity\DxLib\2026夏制作資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDE06467-A1D4-482D-B99C-4AEFA4D5DEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C3235A-79D1-48D8-84F3-4152DC62ED7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="112">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -730,6 +730,13 @@
   </si>
   <si>
     <t>アルファ、ベータ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1263,13 +1270,15 @@
         <v>3</v>
       </c>
       <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
+      <c r="E3" s="14" t="s">
+        <v>111</v>
+      </c>
       <c r="H3" s="14" t="s">
         <v>7</v>
       </c>
       <c r="I3">
         <f>SUMIF(E3:E63,"完了",C3:C63)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L3" t="s">
         <v>8</v>
@@ -1286,28 +1295,30 @@
         <v>3</v>
       </c>
       <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
+      <c r="E4" s="14" t="s">
+        <v>111</v>
+      </c>
       <c r="H4" s="15" t="s">
         <v>11</v>
       </c>
       <c r="I4" s="2">
         <f ca="1">NETWORKDAYS(I5,I6)</f>
-        <v>-9</v>
+        <v>8</v>
       </c>
       <c r="J4" t="s">
         <v>12</v>
       </c>
       <c r="K4" s="3">
         <f ca="1" xml:space="preserve"> I3 / I4</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2">
         <f ca="1">_xlfn.DAYS(I6,I5)</f>
-        <v>-11</v>
+        <v>11</v>
       </c>
       <c r="M4" s="3">
         <f ca="1">I3/L4</f>
-        <v>0</v>
+        <v>2.9090909090909092</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1332,13 +1343,15 @@
         <v>1</v>
       </c>
       <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="E6" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="H6" s="17" t="s">
         <v>16</v>
       </c>
       <c r="I6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1349,7 +1362,9 @@
         <v>1</v>
       </c>
       <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="E7" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="8" spans="1:13">
       <c r="B8" s="9" t="s">
@@ -1359,7 +1374,9 @@
         <v>1</v>
       </c>
       <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="E8" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="9" spans="1:13">
       <c r="B9" s="9" t="s">
@@ -1419,7 +1436,9 @@
         <v>1</v>
       </c>
       <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+      <c r="E13" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="H13" s="13" t="s">
         <v>28</v>
       </c>
@@ -1428,19 +1447,19 @@
       </c>
       <c r="J13" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),I13)</f>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K13" s="3">
         <f ca="1">($I$2 - $I$3) / J13</f>
-        <v>4.4800000000000004</v>
+        <v>8.8888888888888893</v>
       </c>
       <c r="L13">
         <f ca="1">_xlfn.DAYS(I13,$I$6)</f>
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="M13" s="3">
         <f ca="1">($I$2 - $I$3) / L13</f>
-        <v>3.2941176470588234</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1451,7 +1470,9 @@
         <v>2</v>
       </c>
       <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="E14" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="H14" s="18" t="s">
         <v>30</v>
       </c>
@@ -1460,19 +1481,19 @@
       </c>
       <c r="J14" s="2">
         <f t="shared" ref="J14:J15" ca="1" si="0">NETWORKDAYS(TODAY(),I14)</f>
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K14" s="3">
         <f ca="1">($I$2 - $I$3) / J14</f>
-        <v>4</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="L14">
         <f ca="1">_xlfn.DAYS(I14,$I$6)</f>
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="M14" s="3">
         <f ca="1">($I$2 - $I$3) / L14</f>
-        <v>3.0270270270270272</v>
+        <v>5.333333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1492,19 +1513,19 @@
       </c>
       <c r="J15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="K15" s="3">
         <f ca="1">($I$2 - $I$3) / J15</f>
-        <v>3.7333333333333334</v>
+        <v>5.7142857142857144</v>
       </c>
       <c r="L15">
         <f ca="1">_xlfn.DAYS(I15,$I$6)</f>
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="M15" s="3">
         <f ca="1">($I$2 - $I$3) / L15</f>
-        <v>2.7317073170731709</v>
+        <v>4.2105263157894735</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1538,7 +1559,9 @@
         <v>3</v>
       </c>
       <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="E18" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="22" t="s">
@@ -1548,7 +1571,9 @@
         <v>3</v>
       </c>
       <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="E19" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="9" t="s">
@@ -1606,7 +1631,9 @@
         <v>1</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="E25" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="9" t="s">
@@ -1616,7 +1643,9 @@
         <v>2</v>
       </c>
       <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="E26" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="9" t="s">
@@ -1770,7 +1799,9 @@
         <v>2</v>
       </c>
       <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
+      <c r="E42" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="43" spans="2:5">
       <c r="B43" s="9" t="s">
@@ -1780,7 +1811,9 @@
         <v>3</v>
       </c>
       <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
+      <c r="E43" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="44" spans="2:5">
       <c r="B44" s="9" t="s">
@@ -1790,7 +1823,9 @@
         <v>4</v>
       </c>
       <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
+      <c r="E44" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="45" spans="2:5">
       <c r="B45" s="9" t="s">
@@ -1800,7 +1835,9 @@
         <v>2</v>
       </c>
       <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
+      <c r="E45" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="46" spans="2:5">
       <c r="B46" s="9" t="s">
@@ -2258,7 +2295,7 @@
       </c>
       <c r="H4" s="2">
         <f ca="1">NETWORKDAYS(H5,H6)</f>
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
@@ -2269,7 +2306,7 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
-        <v>659</v>
+        <v>681</v>
       </c>
       <c r="L4" s="3">
         <f ca="1">H3/K4</f>
@@ -2303,7 +2340,7 @@
       </c>
       <c r="H6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2382,7 +2419,7 @@
       </c>
       <c r="I13" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),H13)</f>
-        <v>-413</v>
+        <v>-429</v>
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
@@ -2390,7 +2427,7 @@
       </c>
       <c r="K13">
         <f ca="1">_xlfn.DAYS(H13,$H$6)</f>
-        <v>-578</v>
+        <v>-600</v>
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
@@ -2413,7 +2450,7 @@
       </c>
       <c r="I14" s="2">
         <f t="shared" ref="I14:I15" ca="1" si="0">NETWORKDAYS(TODAY(),H14)</f>
-        <v>-393</v>
+        <v>-409</v>
       </c>
       <c r="J14" s="3">
         <f ca="1">($H$2 - $H$3) / I14</f>
@@ -2421,7 +2458,7 @@
       </c>
       <c r="K14">
         <f t="shared" ref="K14:K15" ca="1" si="1">_xlfn.DAYS(H14,$H$6)</f>
-        <v>-550</v>
+        <v>-572</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($H$2 - $H$3) / K14</f>
@@ -2444,7 +2481,7 @@
       </c>
       <c r="I15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-382</v>
+        <v>-398</v>
       </c>
       <c r="J15" s="3">
         <f ca="1">($H$2 - $H$3) / I15</f>
@@ -2452,7 +2489,7 @@
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="1"/>
-        <v>-533</v>
+        <v>-555</v>
       </c>
       <c r="L15" s="3">
         <f ca="1">($H$2 - $H$3) / K15</f>
@@ -3030,12 +3067,59 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3428,65 +3512,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3511,12 +3551,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
-    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/2026夏制作資料/夏制作コスト表.xlsx
+++ b/2026夏制作資料/夏制作コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hirot\Desktop\iroiro\unity\DxLib\2026夏制作資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C3235A-79D1-48D8-84F3-4152DC62ED7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A28B3D2-BCC9-41CF-A3FA-FBC7214021A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="112">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="I3">
         <f>SUMIF(E3:E63,"完了",C3:C63)</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L3" t="s">
         <v>8</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="K4" s="3">
         <f ca="1" xml:space="preserve"> I3 / I4</f>
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="L4" s="2">
         <f ca="1">_xlfn.DAYS(I6,I5)</f>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="M4" s="3">
         <f ca="1">I3/L4</f>
-        <v>2.9090909090909092</v>
+        <v>3.0909090909090908</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="K13" s="3">
         <f ca="1">($I$2 - $I$3) / J13</f>
-        <v>8.8888888888888893</v>
+        <v>8.6666666666666661</v>
       </c>
       <c r="L13">
         <f ca="1">_xlfn.DAYS(I13,$I$6)</f>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M13" s="3">
         <f ca="1">($I$2 - $I$3) / L13</f>
-        <v>6.666666666666667</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="K14" s="3">
         <f ca="1">($I$2 - $I$3) / J14</f>
-        <v>6.666666666666667</v>
+        <v>6.5</v>
       </c>
       <c r="L14">
         <f ca="1">_xlfn.DAYS(I14,$I$6)</f>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="M14" s="3">
         <f ca="1">($I$2 - $I$3) / L14</f>
-        <v>5.333333333333333</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1504,7 +1504,9 @@
         <v>2</v>
       </c>
       <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="E15" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="H15" s="19" t="s">
         <v>32</v>
       </c>
@@ -1517,7 +1519,7 @@
       </c>
       <c r="K15" s="3">
         <f ca="1">($I$2 - $I$3) / J15</f>
-        <v>5.7142857142857144</v>
+        <v>5.5714285714285712</v>
       </c>
       <c r="L15">
         <f ca="1">_xlfn.DAYS(I15,$I$6)</f>
@@ -1525,7 +1527,7 @@
       </c>
       <c r="M15" s="3">
         <f ca="1">($I$2 - $I$3) / L15</f>
-        <v>4.2105263157894735</v>
+        <v>4.1052631578947372</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -3067,59 +3069,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3512,21 +3467,65 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
-    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3551,9 +3550,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/2026夏制作資料/夏制作コスト表.xlsx
+++ b/2026夏制作資料/夏制作コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hirot\Desktop\iroiro\unity\DxLib\2026夏制作資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A28B3D2-BCC9-41CF-A3FA-FBC7214021A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A2DE3B-932B-41E9-A2DF-58F4F98732EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="113">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -736,6 +736,13 @@
     <t>完了</t>
     <rPh sb="0" eb="2">
       <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無し</t>
+    <rPh sb="0" eb="1">
+      <t>ナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1278,7 +1285,7 @@
       </c>
       <c r="I3">
         <f>SUMIF(E3:E63,"完了",C3:C63)</f>
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="L3" t="s">
         <v>8</v>
@@ -1303,22 +1310,22 @@
       </c>
       <c r="I4" s="2">
         <f ca="1">NETWORKDAYS(I5,I6)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J4" t="s">
         <v>12</v>
       </c>
       <c r="K4" s="3">
         <f ca="1" xml:space="preserve"> I3 / I4</f>
-        <v>4.25</v>
+        <v>3.9285714285714284</v>
       </c>
       <c r="L4" s="2">
         <f ca="1">_xlfn.DAYS(I6,I5)</f>
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M4" s="3">
         <f ca="1">I3/L4</f>
-        <v>3.0909090909090908</v>
+        <v>2.8947368421052633</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1351,7 +1358,7 @@
       </c>
       <c r="I6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1386,7 +1393,9 @@
         <v>3</v>
       </c>
       <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="E9" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="10" spans="1:13">
       <c r="B10" s="9" t="s">
@@ -1396,7 +1405,9 @@
         <v>2</v>
       </c>
       <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="E10" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="11" spans="1:13">
       <c r="B11" s="14" t="s">
@@ -1414,7 +1425,9 @@
         <v>1</v>
       </c>
       <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="E12" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="J12" t="s">
         <v>23</v>
       </c>
@@ -1447,19 +1460,19 @@
       </c>
       <c r="J13" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),I13)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K13" s="3">
         <f ca="1">($I$2 - $I$3) / J13</f>
-        <v>8.6666666666666661</v>
+        <v>19</v>
       </c>
       <c r="L13">
         <f ca="1">_xlfn.DAYS(I13,$I$6)</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M13" s="3">
         <f ca="1">($I$2 - $I$3) / L13</f>
-        <v>6.5</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1481,19 +1494,19 @@
       </c>
       <c r="J14" s="2">
         <f t="shared" ref="J14:J15" ca="1" si="0">NETWORKDAYS(TODAY(),I14)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K14" s="3">
         <f ca="1">($I$2 - $I$3) / J14</f>
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="L14">
         <f ca="1">_xlfn.DAYS(I14,$I$6)</f>
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M14" s="3">
         <f ca="1">($I$2 - $I$3) / L14</f>
-        <v>5.2</v>
+        <v>8.1428571428571423</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1515,19 +1528,19 @@
       </c>
       <c r="J15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K15" s="3">
         <f ca="1">($I$2 - $I$3) / J15</f>
-        <v>5.5714285714285712</v>
+        <v>7.125</v>
       </c>
       <c r="L15">
         <f ca="1">_xlfn.DAYS(I15,$I$6)</f>
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="M15" s="3">
         <f ca="1">($I$2 - $I$3) / L15</f>
-        <v>4.1052631578947372</v>
+        <v>5.1818181818181817</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1550,8 +1563,12 @@
       <c r="C17" s="9">
         <v>3</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="D17" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="9" t="s">
@@ -1585,7 +1602,9 @@
         <v>2</v>
       </c>
       <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="E20" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="9" t="s">
@@ -1595,7 +1614,9 @@
         <v>1</v>
       </c>
       <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="E21" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="9" t="s">
@@ -1623,7 +1644,9 @@
         <v>1</v>
       </c>
       <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="E24" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="9" t="s">
@@ -1656,8 +1679,12 @@
       <c r="C27" s="9">
         <v>2</v>
       </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
+      <c r="D27" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="15" t="s">
@@ -1674,8 +1701,12 @@
       <c r="C29" s="9">
         <v>1</v>
       </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="D29" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="9" t="s">
@@ -1684,8 +1715,12 @@
       <c r="C30" s="9">
         <v>1</v>
       </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+      <c r="D30" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="22" t="s">
@@ -1694,8 +1729,12 @@
       <c r="C31" s="9">
         <v>1</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="D31" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="32" spans="2:5">
       <c r="B32" s="9" t="s">
@@ -1704,8 +1743,12 @@
       <c r="C32" s="9">
         <v>2</v>
       </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
+      <c r="D32" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="33" spans="2:5">
       <c r="B33" s="9" t="s">
@@ -1714,8 +1757,12 @@
       <c r="C33" s="9">
         <v>1</v>
       </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
+      <c r="D33" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="34" spans="2:5">
       <c r="B34" s="9" t="s">
@@ -2297,7 +2344,7 @@
       </c>
       <c r="H4" s="2">
         <f ca="1">NETWORKDAYS(H5,H6)</f>
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
@@ -2308,7 +2355,7 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="L4" s="3">
         <f ca="1">H3/K4</f>
@@ -2342,7 +2389,7 @@
       </c>
       <c r="H6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2421,7 +2468,7 @@
       </c>
       <c r="I13" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),H13)</f>
-        <v>-429</v>
+        <v>-435</v>
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
@@ -2429,7 +2476,7 @@
       </c>
       <c r="K13">
         <f ca="1">_xlfn.DAYS(H13,$H$6)</f>
-        <v>-600</v>
+        <v>-608</v>
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
@@ -2452,7 +2499,7 @@
       </c>
       <c r="I14" s="2">
         <f t="shared" ref="I14:I15" ca="1" si="0">NETWORKDAYS(TODAY(),H14)</f>
-        <v>-409</v>
+        <v>-415</v>
       </c>
       <c r="J14" s="3">
         <f ca="1">($H$2 - $H$3) / I14</f>
@@ -2460,7 +2507,7 @@
       </c>
       <c r="K14">
         <f t="shared" ref="K14:K15" ca="1" si="1">_xlfn.DAYS(H14,$H$6)</f>
-        <v>-572</v>
+        <v>-580</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($H$2 - $H$3) / K14</f>
@@ -2483,7 +2530,7 @@
       </c>
       <c r="I15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-398</v>
+        <v>-404</v>
       </c>
       <c r="J15" s="3">
         <f ca="1">($H$2 - $H$3) / I15</f>
@@ -2491,7 +2538,7 @@
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="1"/>
-        <v>-555</v>
+        <v>-563</v>
       </c>
       <c r="L15" s="3">
         <f ca="1">($H$2 - $H$3) / K15</f>
@@ -3069,12 +3116,59 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3467,65 +3561,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3550,12 +3600,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
-    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>